--- a/docs/triton-learning/cards/triton-lesson-10-block-scaled-matmul-oral.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-10-block-scaled-matmul-oral.xlsx
@@ -62,16 +62,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">面试官问：“讲讲块缩放矩阵乘在 B200 上怎么做，换到别的卡会怎样。”以 Triton 教程的 MXFP4 × MXFP4 kernel 为例，用约 60–90 秒讲清：scale 在哪一步乘、怎样排、怎样进到矩阵单元，以及搬到 RTX 5090 和没有块缩放指令的硬件上会怎样。</t>
+          <t xml:space="preserve">面试官问：“讲讲块缩放矩阵乘在 B200 上怎么做，换到别的卡会怎样。”以 Triton 3.7.1 教程的 MXFP4 × MXFP4 kernel 为例，用约 60–90 秒讲清：scale 在哪一步乘、怎样排、怎样进到矩阵单元，以及搬到 RTX 5090 和没有块缩放指令的硬件上会怎样。</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：scale 沿 K 变，只能逐块乘；B200 的 tcgen05.mma 把块 scale 当指令的操作数，在每块的部分和上乘，FP4 的算力全部保住，代价转到了 scale 的布局上。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：scale 沿 K 变，只能逐块乘；B200 的 tcgen05.mma 在指令内部乘块 scale，FP4 的算力全部保住，代价转到了 scale 的布局上。
 • [T#B#怎样排]：tcgen05.mma 要求 scale 在 TMEM 里按 32 个 lane × 4 列排，一个 32 位格子装同一行相邻 4 个 K 块的 scale，所以主机端预排成 (M/128, K/V/4, 32, 4, 4)。
-• [T#B#怎样进去]：5D TMA 把整块搬进 SMEM，一个线程发 tcgen05.cp 原样拷进 TMEM；kernel 里的 reshape、trans 只是 SMEM 描述符上的视图，不搬数据。
-• [T#B#别的卡]：RTX 5090 的 mma.sync 从寄存器读 scale、累加器也在寄存器，要缩小分块；MI355X 从 VGPR 读、只认 E8M0；RTX 4090、H100 走软件换算，解码成 bf16 再用 bf16 张量核；Triton 3.7.1 在 MI300X 上两侧都带 scale 时编译失败。
-[T#B,!c47f17#边界]：预排只关乎性能，不影响结果；格式受指令限制，比如 RTX 5090 不接 FP8 × FP4 混合。</t>
+• [T#B#怎样进去]：TMA 把整块搬进 SMEM，一个线程发 tcgen05.cp 原样拷进 TMEM；kernel 里的 reshape、trans 只是 SMEM 描述符上的视图，不搬数据。
+• [T#B#别的卡]：RTX 5090 的块缩放 mma.sync 从寄存器读 scale、累加器也在寄存器，要缩小分块；MI355X 的 scaled MFMA 从 VGPR 读、只认 E8M0；RTX 4090 没有块缩放指令，解码成 bf16、逐元素乘 scale 再用 bf16 张量核；MI300X 上两侧都带 scale 时编译失败。
+[T#B,!c47f17#边界]：预排只关乎性能，不影响结果；只有一侧带 scale 或格式不受指令支持时，有块缩放指令的卡也会退回软件换算。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -88,21 +88,21 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">请用约 60–90 秒向面试官讲清：在 MI300X 上用 Triton 跑 MoE，专家权重存 bf16，还是存 MXFP4、在 kernel 里解码后用 bf16 MFMA？解码与预填充各怎样判断快慢，怎样量化解码的开销，部署时最终选哪个？</t>
+          <t xml:space="preserve">请用约 60–90 秒向面试官讲清：在 MI300X 上用 Triton 3.7.1 跑 MoE，专家权重存 bf16，还是存 MXFP4、在 kernel 里解码后用 bf16 MFMA？解码与预填充各怎样判断快慢，怎样量化解码的开销，部署时最终选哪个？</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：先拿计算强度和平衡点（约 123 次乘加/字节）比，判断瓶颈；再算显存、MFMA、向量单元各自要忙多久，能重叠就取最长、不能就相加。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：先拿计算强度和平衡点（约 123 次乘加/字节，字节计入激活、权重、scale 和输出）比，判断瓶颈；再算显存、MFMA、向量单元各自要忙多久，能重叠就取最长、不能就相加。
 • [T#B#解码]：M 小，受访存限制，MXFP4 少读约 3.6 倍字节，最多快约 3.6 倍；前提是解码跟得上带宽，每个 FP4 的向量指令要在约 4 条以内。
 • [T#B#预填充]：受计算限制，少读字节换不来时间，MXFP4 最多一样快；解码相对 MFMA 的比例是 16c / BLOCK_M，与 M 无关，藏不住时慢约四成。
 • [T#B#部署]：选 MXFP4：权重小约 3.8 倍，省下的显存给 KV cache，能服务更多请求；并发多了，每个专家的 M 也随之变大。
-[T#B,!c47f17#边界]：强度的单位要和平衡点一致；靠近平衡点、BLOCK_M 变小或 wave 沿 M 排时，解码代价会改变结论，最终要实测。</t>
+[T#B,!c47f17#边界]：每个专家只分到约 128 行时，MXFP4 正好落在平衡点附近，访存和计算都要考虑；BLOCK_M 变小时解码代价会改变结论，最终要实测。</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">用平衡点判断解码与预填充的瓶颈，单位一致；说出解码跟不跟得上带宽的量化判据；说出 16c/BLOCK_M 与 M 无关；说出容量才是始终保留的好处</t>
+          <t xml:space="preserve">用平衡点判断解码与预填充的瓶颈，强度计入全部字节、单位一致；说出解码跟不跟得上带宽的量化判据；说出 16c/BLOCK_M 与 M 无关；说出容量才是始终保留的好处</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -114,7 +114,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">请用约 60–90 秒向面试官讲清你在 RTX 5090 上做的一次受控测量：同一个 MXFP4 kernel 去掉 A 的 scale，迫使 Triton 走软件换算，和原生块缩放指令相比；N = K = 8192，M = 16 与 M = 8192 的结果是什么？怎样解释？你的预测错在哪里？</t>
+          <t xml:space="preserve">请用约 60–90 秒向面试官讲清你在 RTX 5090 上做的一次受控测量：同一个 MXFP4 kernel 去掉 A 的 scale，迫使 Triton 3.7.1 走软件换算，和原生块缩放指令相比；N = K = 8192，M = 16 与 M = 8192 的结果是什么？怎样解释？你的预测错在哪里？</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">

--- a/docs/triton-learning/cards/triton-lesson-10-block-scaled-matmul-oral.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-10-block-scaled-matmul-oral.xlsx
@@ -71,7 +71,7 @@
 • [T#B#怎样排]：tcgen05.mma 要求 scale 在 TMEM 里按 32 个 lane × 4 列排，一个 32 位格子装同一行相邻 4 个 K 块的 scale，所以主机端预排成 (M/128, K/V/4, 32, 4, 4)。
 • [T#B#怎样进去]：TMA 把整块搬进 SMEM，一个线程发 tcgen05.cp 原样拷进 TMEM；kernel 里的 reshape、trans 只是 SMEM 描述符上的视图，不搬数据。
 • [T#B#别的卡]：RTX 5090 的块缩放 mma.sync 从寄存器读 scale、累加器也在寄存器，要缩小分块；MI355X 的 scaled MFMA 从 VGPR 读、只认 E8M0；RTX 4090 没有块缩放指令，解码成 bf16、逐元素乘 scale 再用 bf16 张量核；MI300X 上两侧都带 scale 时编译失败。
-[T#B,!c47f17#边界]：预排只关乎性能，不影响结果；只有一侧带 scale 或格式不受指令支持时，有块缩放指令的卡也会退回软件换算。</t>
+[T#B,!c47f17#边界]：预排只关乎性能，不影响结果；一侧不是低精度格式（如 bf16 × MXFP4），或格式、scale 过不了原生模式的要求（如 RTX 5090 要求两侧都带 scale）时，有块缩放指令的卡也会退回软件换算。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
